--- a/Results/RefMet_name_crosscheck.xlsx
+++ b/Results/RefMet_name_crosscheck.xlsx
@@ -8062,9 +8062,74 @@
           <t>1-O-octadecyl-2-arachidonoyl-sn-glycero-3-phosphocholine</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>PC O-18:0/20:4(5Z,8Z,11Z,14Z)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>C46H86NO7P</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>795.6142</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Glycerophospholipids</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Glycerophosphocholines</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>O-PC</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>GBNPCIWXLWZJGA-IGBSIYCFSA-N</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>6443065</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>75245</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>HMDB0013420</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>LMGP01020102</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>C05212</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>RM0133735</t>
+        </is>
+      </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>No RefMet InChIKey</t>
+          <t>Full match</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -17466,9 +17531,64 @@
           <t>Dilauryl 3,3′-thiodipropionate</t>
         </is>
       </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Didodecyl thiobispropanoate</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>C30H58O4S</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>514.4056</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Fatty Acyls</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>Fatty acids</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Dicarboxylic acids</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>GHKOFFNLGXMVNJ-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>31250</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>165384</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>HMDB0040172</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>RM0153981</t>
+        </is>
+      </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>No RefMet InChIKey</t>
+          <t>Full match</t>
         </is>
       </c>
       <c r="T319" t="inlineStr">
@@ -19348,9 +19468,64 @@
           <t>1-linoleoyl-sn-glycero-3-phosphoethanolamine</t>
         </is>
       </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>LPE 18:2(9Z,12Z)/0:0</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>C23H44NO7P</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>477.2855</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Glycerophospholipids</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>Glycerophosphoethanolamines</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>LPE</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>DBHKHNGBVGWQJE-USWSLJGRSA-M</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>134726037</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>83058</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>C04438</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>RM0133422</t>
+        </is>
+      </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>No RefMet InChIKey</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T373" t="inlineStr">
@@ -26062,9 +26237,64 @@
           <t>1-linoleoyl-sn-glycero-3-phosphoethanolamine</t>
         </is>
       </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>LPE 18:2(9Z,12Z)/0:0</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>C23H44NO7P</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>477.2855</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Glycerophospholipids</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>Glycerophosphoethanolamines</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>LPE</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>DBHKHNGBVGWQJE-USWSLJGRSA-M</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>134726037</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>83058</t>
+        </is>
+      </c>
+      <c r="Q531" t="inlineStr">
+        <is>
+          <t>C04438</t>
+        </is>
+      </c>
+      <c r="R531" t="inlineStr">
+        <is>
+          <t>RM0133422</t>
+        </is>
+      </c>
       <c r="S531" t="inlineStr">
         <is>
-          <t>No RefMet InChIKey</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T531" t="inlineStr">
@@ -28861,9 +29091,59 @@
           <t>7-Methyl-2,6,9,12-tetraoxahexadecane</t>
         </is>
       </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>alpha-Butyl-omega-hydroxypoly(oxyethylene) poly(oxypropylene)</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>C13H28O4</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>248.1988</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>Organic oxygen compounds</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>Ethers</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Polyethylene glycols</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>PXWCUJRVSZCPHE-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>24838540</t>
+        </is>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>HMDB0032181</t>
+        </is>
+      </c>
+      <c r="R599" t="inlineStr">
+        <is>
+          <t>RM0234042</t>
+        </is>
+      </c>
       <c r="S599" t="inlineStr">
         <is>
-          <t>No RefMet InChIKey</t>
+          <t>Full match</t>
         </is>
       </c>
       <c r="T599" t="inlineStr">
@@ -56715,7 +56995,7 @@
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>(1R,9S,12S,13R,14S,17R,18Z,21S,23S,24S,25S,27R)-17-Allyl-1,14,25-trihydroxy-12-{(1E)-1-[(1R,3R,4R)-4-hydroxy-3-methoxycyclohexyl]-1-propen-2-yl}-23-methoxy-13,19,21,27-tetramethyl-11,28-dioxa-4-azatri_x000D_
+          <t>(1R,9S,12S,13R,14S,17R,18Z,21S,23S,24S,25S,27R)-17-Allyl-1,14,25-trihydroxy-12-{(1E)-1-[(1R,3R,4R)-4-hydroxy-3-methoxycyclohexyl]-1-propen-2-yl}-23-methoxy-13,19,21,27-tetramethyl-11,28-dioxa-4-azatri_x000D__x000D__x000D_
 cyclo[22.3.1.0~4,9~]octacos-18-ene-2,3,10,16-tetrone</t>
         </is>
       </c>
@@ -59698,7 +59978,7 @@
       </c>
       <c r="B1673" t="inlineStr">
         <is>
-          <t>(3R,4S,5S,6R,7R,9R,11R,12R,13S,14R)-6-{[(2S,3R,4S,6R)-4-(Dimethylamino)-3-hydroxy-6-methyltetrahydro-2H-pyran-2-yl]oxy}-12,13-dihydroxy-14-[(1S)-1-hydroxyethyl]-4-{[(2R,4R,5S,6S)-5-hydroxy-4-methoxy-4_x000D_
+          <t>(3R,4S,5S,6R,7R,9R,11R,12R,13S,14R)-6-{[(2S,3R,4S,6R)-4-(Dimethylamino)-3-hydroxy-6-methyltetrahydro-2H-pyran-2-yl]oxy}-12,13-dihydroxy-14-[(1S)-1-hydroxyethyl]-4-{[(2R,4R,5S,6S)-5-hydroxy-4-methoxy-4_x000D__x000D__x000D_
 ,6-dimethyltetrahydro-2H-pyran-2-yl]oxy}-7-methoxy-3,5,7,9,11,13-hexamethyloxacyclotetradecane-2,10-dione</t>
         </is>
       </c>
@@ -61664,7 +61944,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T94"/>
+  <dimension ref="A1:T96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -64732,16 +65012,16 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3,4-Dihydroxybenzenesulfonic acid</t>
+          <t>1-linoleoyl-sn-glycero-3-phosphoethanolamine</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FPXPQMOQWJZYBL-UHFFFAOYSA-N</t>
+          <t>DBHKHNGBVGWQJE-USWSLJGRSA-N</t>
         </is>
       </c>
       <c r="D34">
@@ -64749,62 +65029,67 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3,4-Dihydroxybenzenesulfonic acid</t>
+          <t>1-linoleoyl-sn-glycero-3-phosphoethanolamine</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3,4-Dihydroxybenzenesulfonic acid</t>
+          <t>LPE 18:2(9Z,12Z)/0:0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C6H6O5S</t>
+          <t>C23H44NO7P</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>189.9936</t>
+          <t>477.2855</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Benzenoids</t>
+          <t>Glycerophospholipids</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Benzenes</t>
+          <t>Glycerophosphoethanolamines</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Benzenesulfonyl compounds</t>
+          <t>LPE</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>LTPDITOEDOAWRU-UHFFFAOYSA-N</t>
+          <t>DBHKHNGBVGWQJE-USWSLJGRSA-M</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>189003</t>
+          <t>134726037</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>27758</t>
+          <t>83058</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>C04438</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>RM0037269</t>
+          <t>RM0133422</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -64815,79 +65100,74 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tetranor-12R-HETE</t>
+          <t>3,4-Dihydroxybenzenesulfonic acid</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ASETYIALRXDVDF-UHFFFAOYSA-N</t>
+          <t>FPXPQMOQWJZYBL-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tetranor-12R-HETE</t>
+          <t>3,4-Dihydroxybenzenesulfonic acid</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tetranor-12R-HETE</t>
+          <t>3,4-Dihydroxybenzenesulfonic acid</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C16H26O3</t>
+          <t>C6H6O5S</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>266.1882</t>
+          <t>189.9936</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Fatty Acyls</t>
+          <t>Benzenoids</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Eicosanoids</t>
+          <t>Benzenes</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>HETE</t>
+          <t>Benzenesulfonyl compounds</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>KBOVKDIBOBQLRS-QCNAHCIUSA-N</t>
+          <t>LTPDITOEDOAWRU-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>5282970</t>
+          <t>189003</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>72605</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>LMFA01050143</t>
+          <t>27758</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>RM0153662</t>
+          <t>RM0037269</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -64903,16 +65183,16 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10-HDA</t>
+          <t>Tetranor-12R-HETE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ZHYZQXUYZJNEHD-UHFFFAOYSA-N</t>
+          <t>ASETYIALRXDVDF-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D36">
@@ -64920,22 +65200,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10-HDA</t>
+          <t>Tetranor-12R-HETE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10-Hydroxy-2E-decenoic acid</t>
+          <t>Tetranor-12R-HETE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C10H18O3</t>
+          <t>C16H26O3</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>186.1256</t>
+          <t>266.1882</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -64945,37 +65225,37 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Fatty acids</t>
+          <t>Eicosanoids</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Hydroxy FA</t>
+          <t>HETE</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>QHBZHVUGQROELI-SOFGYWHQSA-N</t>
+          <t>KBOVKDIBOBQLRS-QCNAHCIUSA-N</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>5312738</t>
+          <t>5282970</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>78668</t>
+          <t>72605</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>LMFA01050157</t>
+          <t>LMFA01050143</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>RM0194332</t>
+          <t>RM0153662</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -64991,16 +65271,16 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Decanoylcarnitine</t>
+          <t>10-HDA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LZOSYCMHQXPBFU-UHFFFAOYSA-N</t>
+          <t>ZHYZQXUYZJNEHD-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D37">
@@ -65008,22 +65288,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Decanoylcarnitine</t>
+          <t>10-HDA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CAR 10:0</t>
+          <t>10-Hydroxy-2E-decenoic acid</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C17H33NO4</t>
+          <t>C10H18O3</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>315.241</t>
+          <t>186.1256</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -65033,52 +65313,42 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Fatty esters</t>
+          <t>Fatty acids</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Acyl carnitines</t>
+          <t>Hydroxy FA</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>LZOSYCMHQXPBFU-OAHLLOKOSA-N</t>
+          <t>QHBZHVUGQROELI-SOFGYWHQSA-N</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>11953821</t>
+          <t>5312738</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>28717</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>HMDB0000651</t>
+          <t>78668</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>LMFA07070006</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>C03299</t>
+          <t>LMFA01050157</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>RM0153849</t>
+          <t>RM0194332</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Connectivity match</t>
+          <t>Mismatch</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -65089,16 +65359,16 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>444</v>
+        <v>419</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lyso-PAF C-18</t>
+          <t>Decanoylcarnitine</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>XKBJVQHMEXMFDZ-UHFFFAOYSA-N</t>
+          <t>LZOSYCMHQXPBFU-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D38">
@@ -65106,72 +65376,72 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lyso-PAF C-18</t>
+          <t>Decanoylcarnitine</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>LPC O-18:0</t>
+          <t>CAR 10:0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C26H56NO6P</t>
+          <t>C17H33NO4</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>509.3845</t>
+          <t>315.241</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Glycerophospholipids</t>
+          <t>Fatty Acyls</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Glycerophosphocholines</t>
+          <t>Fatty esters</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O-LPC</t>
+          <t>Acyl carnitines</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>XKBJVQHMEXMFDZ-AREMUKBSSA-N</t>
+          <t>LZOSYCMHQXPBFU-OAHLLOKOSA-N</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2733532</t>
+          <t>11953821</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>75216</t>
+          <t>28717</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>HMDB0011149</t>
+          <t>HMDB0000651</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>LMGP01060014</t>
+          <t>LMFA07070006</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>C04317</t>
+          <t>C03299</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>RM0135072</t>
+          <t>RM0153849</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -65187,16 +65457,16 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ACPC</t>
+          <t>Lyso-PAF C-18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PAJPWUMXBYXFCZ-UHFFFAOYSA-N</t>
+          <t>XKBJVQHMEXMFDZ-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D39">
@@ -65204,72 +65474,77 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ACPC</t>
+          <t>Lyso-PAF C-18</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cyclacillin</t>
+          <t>LPC O-18:0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C15H23N3O4S</t>
+          <t>C26H56NO6P</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>341.1409</t>
+          <t>509.3845</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Organoheterocyclic compounds</t>
+          <t>Glycerophospholipids</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Beta lactams</t>
+          <t>Glycerophosphocholines</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Penicillins</t>
+          <t>O-LPC</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>HGBLNBBNRORJKI-WCABBAIRSA-N</t>
+          <t>XKBJVQHMEXMFDZ-AREMUKBSSA-N</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>19003</t>
+          <t>2733532</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>75216</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>HMDB0015135</t>
+          <t>HMDB0011149</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>LMGP01060014</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>C12766</t>
+          <t>C04317</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>RM0118018</t>
+          <t>RM0135072</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -65280,16 +65555,16 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5-hydroxy-4-methoxy-5,6-dihydro-2H-pyran-2-one</t>
+          <t>ACPC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LDCRTTXIJACKKU-ARJAWSKDSA-N</t>
+          <t>PAJPWUMXBYXFCZ-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D40">
@@ -65297,22 +65572,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5-hydroxy-4-methoxy-5,6-dihydro-2H-pyran-2-one</t>
+          <t>ACPC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>5-Hydroxy-4-methoxy-5,6-dihydro-2H-pyran-2-one</t>
+          <t>Cyclacillin</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>C6H8O4</t>
+          <t>C15H23N3O4S</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>144.0423</t>
+          <t>341.1409</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -65322,32 +65597,42 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Pyrans</t>
+          <t>Beta lactams</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Pyranones</t>
+          <t>Penicillins</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>PBEXSRJMCVDBFK-UHFFFAOYSA-N</t>
+          <t>HGBLNBBNRORJKI-WCABBAIRSA-N</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>56773935</t>
+          <t>19003</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>183447</t>
+          <t>31444</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>HMDB0015135</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>C12766</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>RM0161253</t>
+          <t>RM0118018</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -65363,16 +65648,16 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>476</v>
+        <v>456</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8-Amino-7-oxononanoic acid</t>
+          <t>5-hydroxy-4-methoxy-5,6-dihydro-2H-pyran-2-one</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GUAHPAJOXVYFON-UHFFFAOYSA-N</t>
+          <t>LDCRTTXIJACKKU-ARJAWSKDSA-N</t>
         </is>
       </c>
       <c r="D41">
@@ -65380,77 +65665,62 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8-Amino-7-oxononanoic acid</t>
+          <t>5-hydroxy-4-methoxy-5,6-dihydro-2H-pyran-2-one</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>8-Amino-7-oxononanoic acid</t>
+          <t>5-Hydroxy-4-methoxy-5,6-dihydro-2H-pyran-2-one</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C9H17NO3</t>
+          <t>C6H8O4</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>187.1208</t>
+          <t>144.0423</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Fatty Acyls</t>
+          <t>Organoheterocyclic compounds</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Fatty acids</t>
+          <t>Pyrans</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Keto FA</t>
+          <t>Pyranones</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>GUAHPAJOXVYFON-ZETCQYMHSA-N</t>
+          <t>PBEXSRJMCVDBFK-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>448124</t>
+          <t>56773935</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>15830</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>HMDB0240687</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>LMFA01100065</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>C01092</t>
+          <t>183447</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>RM0155766</t>
+          <t>RM0161253</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Connectivity match</t>
+          <t>Mismatch</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -65461,84 +65731,89 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>501</v>
+        <v>476</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>cuscohygrine</t>
+          <t>8-Amino-7-oxononanoic acid</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ZEBIACKKLGVLFZ-UHFFFAOYSA-N</t>
+          <t>GUAHPAJOXVYFON-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>cuscohygrine</t>
+          <t>8-Amino-7-oxononanoic acid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cuscohygrine</t>
+          <t>8-Amino-7-oxononanoic acid</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>C13H24N2O</t>
+          <t>C9H17NO3</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>224.1889</t>
+          <t>187.1208</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Alkaloids</t>
+          <t>Fatty Acyls</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Alkaloids</t>
+          <t>Fatty acids</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Other alkaloids</t>
+          <t>Keto FA</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ZEBIACKKLGVLFZ-TXEJJXNPSA-N</t>
+          <t>GUAHPAJOXVYFON-ZETCQYMHSA-N</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1201543</t>
+          <t>448124</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>27920</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>HMDB0030290</t>
+          <t>HMDB0240687</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>LMFA01100065</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>C06521</t>
+          <t>C01092</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>RM0136873</t>
+          <t>RM0155766</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -65554,16 +65829,16 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sinapyl alcohol</t>
+          <t>cuscohygrine</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LZFOPEXOUVTGJS-ONEGZZNKSA-N</t>
+          <t>ZEBIACKKLGVLFZ-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D43">
@@ -65571,67 +65846,67 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sinapyl alcohol</t>
+          <t>cuscohygrine</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sinapyl alcohol</t>
+          <t>Cuscohygrine</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>C11H14O4</t>
+          <t>C13H24N2O</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>210.0892</t>
+          <t>224.1889</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Alkaloids</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Phenylpropanoids</t>
+          <t>Alkaloids</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Cinnamic acids</t>
+          <t>Other alkaloids</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>LZFOPEXOUVTGJS-UHFFFAOYSA-N</t>
+          <t>ZEBIACKKLGVLFZ-TXEJJXNPSA-N</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>5280507</t>
+          <t>1201543</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>28813</t>
+          <t>27920</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>HMDB0013070</t>
+          <t>HMDB0030290</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>C02325</t>
+          <t>C06521</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>RM0027534</t>
+          <t>RM0136873</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -65647,16 +65922,16 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10-HDA</t>
+          <t>Sinapyl alcohol</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ZHYZQXUYZJNEHD-UHFFFAOYSA-N</t>
+          <t>LZFOPEXOUVTGJS-ONEGZZNKSA-N</t>
         </is>
       </c>
       <c r="D44">
@@ -65664,67 +65939,72 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>10-HDA</t>
+          <t>Sinapyl alcohol</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10-Hydroxy-2E-decenoic acid</t>
+          <t>Sinapyl alcohol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C10H18O3</t>
+          <t>C11H14O4</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>186.1256</t>
+          <t>210.0892</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Fatty Acyls</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Fatty acids</t>
+          <t>Phenylpropanoids</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Hydroxy FA</t>
+          <t>Cinnamic acids</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>QHBZHVUGQROELI-SOFGYWHQSA-N</t>
+          <t>LZFOPEXOUVTGJS-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>5312738</t>
+          <t>5280507</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>78668</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>LMFA01050157</t>
+          <t>28813</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>HMDB0013070</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>C02325</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>RM0194332</t>
+          <t>RM0027534</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -65735,16 +66015,16 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>trans-4-Hydroxy-L-proline</t>
+          <t>10-HDA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PMMYEEVYMWASQN-UHFFFAOYSA-N</t>
+          <t>ZHYZQXUYZJNEHD-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D45">
@@ -65752,72 +66032,67 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>trans-4-Hydroxy-L-proline</t>
+          <t>10-HDA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>trans-4-Hydroxyproline</t>
+          <t>10-Hydroxy-2E-decenoic acid</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>C5H9NO3</t>
+          <t>C10H18O3</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>131.0582</t>
+          <t>186.1256</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Fatty Acyls</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Amino acids and peptides</t>
+          <t>Fatty acids</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Amino acids</t>
+          <t>Hydroxy FA</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>PMMYEEVYMWASQN-DMTCNVIQSA-N</t>
+          <t>QHBZHVUGQROELI-SOFGYWHQSA-N</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>5312738</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>18095</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>HMDB0000725</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>C01157</t>
+          <t>78668</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>LMFA01050157</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>RM0128618</t>
+          <t>RM0194332</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Connectivity match</t>
+          <t>Mismatch</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -65828,16 +66103,16 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4-Indolecarbaldehyde</t>
+          <t>trans-4-Hydroxy-L-proline</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OLNJUISKUQQNIM-UHFFFAOYSA-N</t>
+          <t>PMMYEEVYMWASQN-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D46">
@@ -65845,62 +66120,72 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4-Indolecarbaldehyde</t>
+          <t>trans-4-Hydroxy-L-proline</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Indole-4-carboxaldehyde</t>
+          <t>trans-4-Hydroxyproline</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>C9H7NO</t>
+          <t>C5H9NO3</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>145.0528</t>
+          <t>131.0582</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Alkaloids</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Tryptophan alkaloids</t>
+          <t>Amino acids and peptides</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Simple indole alkaloids</t>
+          <t>Amino acids</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>JFDDFGLNZWNJTK-UHFFFAOYSA-N</t>
+          <t>PMMYEEVYMWASQN-DMTCNVIQSA-N</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>333703</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>143235</t>
+          <t>18095</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>HMDB0000725</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>C01157</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>RM0011479</t>
+          <t>RM0128618</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -65911,16 +66196,16 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fumaric acid</t>
+          <t>4-Indolecarbaldehyde</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VZCYOOQTPOCHFL-UPHRSURJSA-N</t>
+          <t>OLNJUISKUQQNIM-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D47">
@@ -65928,72 +66213,62 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fumaric acid</t>
+          <t>4-Indolecarbaldehyde</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fumaric acid</t>
+          <t>Indole-4-carboxaldehyde</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>C4H4O4</t>
+          <t>C9H7NO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>116.011</t>
+          <t>145.0528</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Alkaloids</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>TCA acids</t>
+          <t>Tryptophan alkaloids</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>TCA acids</t>
+          <t>Simple indole alkaloids</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>VZCYOOQTPOCHFL-OWOJBTEDSA-N</t>
+          <t>JFDDFGLNZWNJTK-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>444972</t>
+          <t>333703</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>18012</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>HMDB0000134</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>C00122</t>
+          <t>143235</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>RM0135891</t>
+          <t>RM0011479</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Connectivity match</t>
+          <t>Mismatch</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -66004,16 +66279,16 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>N-Benzylformamide</t>
+          <t>1-linoleoyl-sn-glycero-3-phosphoethanolamine</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FZERHIULMFGESH-UHFFFAOYSA-N</t>
+          <t>DBHKHNGBVGWQJE-USWSLJGRSA-N</t>
         </is>
       </c>
       <c r="D48">
@@ -66021,67 +66296,67 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>N-Benzylformamide</t>
+          <t>1-linoleoyl-sn-glycero-3-phosphoethanolamine</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>N-benzylformamide</t>
+          <t>LPE 18:2(9Z,12Z)/0:0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C8H9NO</t>
+          <t>C23H44NO7P</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>135.0684</t>
+          <t>477.2855</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Benzenoids</t>
+          <t>Glycerophospholipids</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Benzenes</t>
+          <t>Glycerophosphoethanolamines</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Other benzenes</t>
+          <t>LPE</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>IIBOGKHTXBPGEI-UHFFFAOYSA-N</t>
+          <t>DBHKHNGBVGWQJE-USWSLJGRSA-M</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>80654</t>
+          <t>134726037</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>41117</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>HMDB0304423</t>
+          <t>83058</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>C04438</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>RM0156532</t>
+          <t>RM0133422</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -66092,16 +66367,16 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Prolylleucine</t>
+          <t>Fumaric acid</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VTJUNIYRYIAIHF-UHFFFAOYSA-N</t>
+          <t>VZCYOOQTPOCHFL-UPHRSURJSA-N</t>
         </is>
       </c>
       <c r="D49">
@@ -66109,22 +66384,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Prolylleucine</t>
+          <t>Fumaric acid</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pro-Leu</t>
+          <t>Fumaric acid</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C11H20N2O3</t>
+          <t>C4H4O4</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>228.1474</t>
+          <t>116.011</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -66134,42 +66409,47 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Amino acids and peptides</t>
+          <t>TCA acids</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Dipeptides</t>
+          <t>TCA acids</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ZKQOUHVVXABNDG-IUCAKERBSA-N</t>
+          <t>VZCYOOQTPOCHFL-OWOJBTEDSA-N</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>444109</t>
+          <t>444972</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>74791</t>
+          <t>18012</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>HMDB0253028</t>
+          <t>HMDB0000134</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>C00122</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>RM0137550</t>
+          <t>RM0135891</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -66180,16 +66460,16 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DL-Citrulline</t>
+          <t>N-Benzylformamide</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>RHGKLRLOHDJJDR-UHFFFAOYSA-N</t>
+          <t>FZERHIULMFGESH-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D50">
@@ -66197,72 +66477,67 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>DL-Citrulline</t>
+          <t>N-Benzylformamide</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Citrulline</t>
+          <t>N-benzylformamide</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>C6H13N3O3</t>
+          <t>C8H9NO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>175.0957</t>
+          <t>135.0684</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Benzenoids</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Amino acids and peptides</t>
+          <t>Benzenes</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Amino acids</t>
+          <t>Other benzenes</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>RHGKLRLOHDJJDR-BYPYZUCNSA-N</t>
+          <t>IIBOGKHTXBPGEI-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>80654</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>18211</t>
+          <t>41117</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>HMDB0000904</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>C00327</t>
+          <t>HMDB0304423</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>RM0136022</t>
+          <t>RM0156532</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Connectivity match</t>
+          <t>Mismatch</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -66273,16 +66548,16 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>L-Aspartic acid</t>
+          <t>Prolylleucine</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CKLJMWTZIZZHCS-UHFFFAOYSA-N</t>
+          <t>VTJUNIYRYIAIHF-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D51">
@@ -66290,22 +66565,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>L-Aspartic acid</t>
+          <t>Prolylleucine</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aspartic acid</t>
+          <t>Pro-Leu</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>C4H7NO4</t>
+          <t>C11H20N2O3</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>133.0375</t>
+          <t>228.1474</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -66320,42 +66595,37 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Amino acids</t>
+          <t>Dipeptides</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CKLJMWTZIZZHCS-REOHCLBHSA-N</t>
+          <t>ZKQOUHVVXABNDG-IUCAKERBSA-N</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>444109</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>22660</t>
+          <t>74791</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>HMDB0000191</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>C00049</t>
+          <t>HMDB0253028</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>RM0135905</t>
+          <t>RM0137550</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Connectivity match</t>
+          <t>Mismatch</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -66366,16 +66636,16 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Butyl benzoate</t>
+          <t>DL-Citrulline</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VONGZNXBKCOUHB-UHFFFAOYSA-N</t>
+          <t>RHGKLRLOHDJJDR-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D52">
@@ -66383,67 +66653,72 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Butyl benzoate</t>
+          <t>DL-Citrulline</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Butyl benzoate</t>
+          <t>Citrulline</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C11H14O2</t>
+          <t>C6H13N3O3</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>178.0994</t>
+          <t>175.0957</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Benzenoids</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Benzoic acids</t>
+          <t>Amino acids and peptides</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Benzoic acid esters</t>
+          <t>Amino acids</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>XSIFPSYPOVKYCO-UHFFFAOYSA-N</t>
+          <t>RHGKLRLOHDJJDR-BYPYZUCNSA-N</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>156070</t>
+          <t>18211</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>HMDB0303178</t>
+          <t>HMDB0000904</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>C00327</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>RM0199266</t>
+          <t>RM0136022</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -66454,69 +66729,84 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>610</v>
+        <v>565</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Farnesyl acetate</t>
+          <t>L-Aspartic acid</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ZGIGZINMAOQWLX-NCZFFCEISA-N</t>
+          <t>CKLJMWTZIZZHCS-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D53">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Farnesyl acetate</t>
+          <t>L-Aspartic acid</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Farnesyl acetate</t>
+          <t>Aspartic acid</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>C17H28O2</t>
+          <t>C4H7NO4</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>264.2089</t>
+          <t>133.0375</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Prenol Lipids</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Isoprenoids</t>
+          <t>Amino acids and peptides</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>C15 isoprenoids</t>
+          <t>Amino acids</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>ZGIGZINMAOQWLX-UHFFFAOYSA-N</t>
+          <t>CKLJMWTZIZZHCS-REOHCLBHSA-N</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>94403</t>
+          <t>5960</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>22660</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>HMDB0000191</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>C00049</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>RM0202841</t>
+          <t>RM0135905</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -66532,89 +66822,84 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>633</v>
+        <v>579</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>L-Lysine</t>
+          <t>Butyl benzoate</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KDXKERNSBIXSRK-UHFFFAOYSA-N</t>
+          <t>VONGZNXBKCOUHB-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>L-Lysine</t>
+          <t>Butyl benzoate</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lysine</t>
+          <t>Butyl benzoate</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C6H14N2O2</t>
+          <t>C11H14O2</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>146.1055</t>
+          <t>178.0994</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Benzenoids</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Amino acids and peptides</t>
+          <t>Benzoic acids</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Amino acids</t>
+          <t>Benzoic acid esters</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>KDXKERNSBIXSRK-YFKPBYRVSA-N</t>
+          <t>XSIFPSYPOVKYCO-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>25094</t>
+          <t>156070</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>HMDB0000182</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>C00047</t>
+          <t>HMDB0303178</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>RM0135903</t>
+          <t>RM0199266</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Connectivity match</t>
+          <t>Mismatch</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -66625,16 +66910,16 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>657</v>
+        <v>610</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>trans-3-Hydroxycotinine</t>
+          <t>Farnesyl acetate</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>XOKCJXZZNAUIQN-IENPIDJESA-N</t>
+          <t>ZGIGZINMAOQWLX-NCZFFCEISA-N</t>
         </is>
       </c>
       <c r="D55">
@@ -66642,62 +66927,52 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>trans-3-Hydroxycotinine</t>
+          <t>Farnesyl acetate</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>trans-3-Hydroxycotinine</t>
+          <t>Farnesyl acetate</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>C10H12N2O2</t>
+          <t>C17H28O2</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>192.0899</t>
+          <t>264.2089</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Alkaloids</t>
+          <t>Prenol Lipids</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Alkaloids</t>
+          <t>Isoprenoids</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Other alkaloids</t>
+          <t>C15 isoprenoids</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>XOKCJXZZNAUIQN-DTWKUNHWSA-N</t>
+          <t>ZGIGZINMAOQWLX-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>107963</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>71182</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>HMDB0001390</t>
+          <t>94403</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>RM0159961</t>
+          <t>RM0202841</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -66713,16 +66988,16 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>667</v>
+        <v>633</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dambonitol</t>
+          <t>L-Lysine</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MMCIFJWGSIWJLP-RRNBHUGPSA-N</t>
+          <t>KDXKERNSBIXSRK-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D56">
@@ -66730,62 +67005,67 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dambonitol</t>
+          <t>L-Lysine</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dambonitol</t>
+          <t>Lysine</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>C8H16O6</t>
+          <t>C6H14N2O2</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>208.0947</t>
+          <t>146.1055</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Organic oxygen compounds</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Alcohols and polyols</t>
+          <t>Amino acids and peptides</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Cyclitols</t>
+          <t>Amino acids</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>MMCIFJWGSIWJLP-XAMPRYAMSA-N</t>
+          <t>KDXKERNSBIXSRK-YFKPBYRVSA-N</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>21627888</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>173588</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>HMDB0033942</t>
+          <t>HMDB0000182</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>C00047</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>RM0224280</t>
+          <t>RM0135903</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -66801,16 +67081,16 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>L(+)-Ornithine</t>
+          <t>trans-3-Hydroxycotinine</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AHLPHDHHMVZTML-UHFFFAOYSA-N</t>
+          <t>XOKCJXZZNAUIQN-IENPIDJESA-N</t>
         </is>
       </c>
       <c r="D57">
@@ -66818,67 +67098,62 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>L(+)-Ornithine</t>
+          <t>trans-3-Hydroxycotinine</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ornithine</t>
+          <t>trans-3-Hydroxycotinine</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>C5H12N2O2</t>
+          <t>C10H12N2O2</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>132.0899</t>
+          <t>192.0899</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Alkaloids</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Amino acids and peptides</t>
+          <t>Alkaloids</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Amino acids</t>
+          <t>Other alkaloids</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>AHLPHDHHMVZTML-BYPYZUCNSA-N</t>
+          <t>XOKCJXZZNAUIQN-DTWKUNHWSA-N</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>107963</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>18257</t>
+          <t>71182</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>HMDB0000214</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>C00077</t>
+          <t>HMDB0001390</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>RM0135912</t>
+          <t>RM0159961</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -66894,16 +67169,16 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Trp-Phe</t>
+          <t>Dambonitol</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IMMPMHKLUUZKAZ-UHFFFAOYSA-N</t>
+          <t>MMCIFJWGSIWJLP-RRNBHUGPSA-N</t>
         </is>
       </c>
       <c r="D58">
@@ -66911,62 +67186,62 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Trp-Phe</t>
+          <t>Dambonitol</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trp-Phe</t>
+          <t>Dambonitol</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C20H21N3O3</t>
+          <t>C8H16O6</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>351.1583</t>
+          <t>208.0947</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Organic oxygen compounds</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Amino acids and peptides</t>
+          <t>Alcohols and polyols</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Dipeptides</t>
+          <t>Cyclitols</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>IMMPMHKLUUZKAZ-WMZOPIPTSA-N</t>
+          <t>MMCIFJWGSIWJLP-XAMPRYAMSA-N</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>6426942</t>
+          <t>21627888</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>74874</t>
+          <t>173588</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>HMDB0029090</t>
+          <t>HMDB0033942</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>RM0022955</t>
+          <t>RM0224280</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -66982,79 +67257,89 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>753</v>
+        <v>668</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4-Indolecarbaldehyde</t>
+          <t>L(+)-Ornithine</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OLNJUISKUQQNIM-UHFFFAOYSA-N</t>
+          <t>AHLPHDHHMVZTML-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D59">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4-Indolecarbaldehyde</t>
+          <t>L(+)-Ornithine</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Indole-4-carboxaldehyde</t>
+          <t>Ornithine</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>C9H7NO</t>
+          <t>C5H12N2O2</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>145.0528</t>
+          <t>132.0899</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Alkaloids</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Tryptophan alkaloids</t>
+          <t>Amino acids and peptides</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Simple indole alkaloids</t>
+          <t>Amino acids</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>JFDDFGLNZWNJTK-UHFFFAOYSA-N</t>
+          <t>AHLPHDHHMVZTML-BYPYZUCNSA-N</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>333703</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>143235</t>
+          <t>18257</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>HMDB0000214</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>C00077</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>RM0011479</t>
+          <t>RM0135912</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -67065,39 +67350,39 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>763</v>
+        <v>673</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ibuprofen</t>
+          <t>Trp-Phe</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HEFNNWSXXWATRW-UHFFFAOYSA-N</t>
+          <t>IMMPMHKLUUZKAZ-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D60">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ibuprofen</t>
+          <t>Trp-Phe</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ibuprofen</t>
+          <t>Trp-Phe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C13H18O2</t>
+          <t>C20H21N3O3</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>206.1307</t>
+          <t>351.1583</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -67107,42 +67392,37 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Phenylpropanoids</t>
+          <t>Amino acids and peptides</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Cinnamic acids</t>
+          <t>Dipeptides</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>HEFNNWSXXWATRW-SNVBAGLBSA-N</t>
+          <t>IMMPMHKLUUZKAZ-WMZOPIPTSA-N</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>114864</t>
+          <t>6426942</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>74874</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>HMDB0001925</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>C01588</t>
+          <t>HMDB0029090</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>RM0052815</t>
+          <t>RM0022955</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -67158,84 +67438,79 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>808</v>
+        <v>753</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>geranial</t>
+          <t>4-Indolecarbaldehyde</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>WTEVQBCEXWBHNA-JXMROGBWSA-N</t>
+          <t>OLNJUISKUQQNIM-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D61">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>geranial</t>
+          <t>4-Indolecarbaldehyde</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Citral</t>
+          <t>Indole-4-carboxaldehyde</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C10H16O</t>
+          <t>C9H7NO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>152.1201</t>
+          <t>145.0528</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Prenol Lipids</t>
+          <t>Alkaloids</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Isoprenoids</t>
+          <t>Tryptophan alkaloids</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>C10 isoprenoids</t>
+          <t>Simple indole alkaloids</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>WTEVQBCEXWBHNA-UHFFFAOYSA-N</t>
+          <t>JFDDFGLNZWNJTK-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>333703</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>23316</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>HMDB0250303</t>
+          <t>143235</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>RM0015070</t>
+          <t>RM0011479</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Connectivity match</t>
+          <t>Mismatch</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -67246,89 +67521,89 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>830</v>
+        <v>763</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Acetylcholine</t>
+          <t>Ibuprofen</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>JHPNVNIEXXLNTR-UHFFFAOYSA-N</t>
+          <t>HEFNNWSXXWATRW-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D62">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Acetylcholine</t>
+          <t>Ibuprofen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Acetylcholine</t>
+          <t>Ibuprofen</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>C7H16NO2</t>
+          <t>C13H18O2</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>146.1181</t>
+          <t>206.1307</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Organic nitrogen compounds</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Cholines</t>
+          <t>Phenylpropanoids</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Acyl cholines</t>
+          <t>Cinnamic acids</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>OIPILFWXSMYKGL-UHFFFAOYSA-N</t>
+          <t>HEFNNWSXXWATRW-SNVBAGLBSA-N</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>114864</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>15355</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>HMDB0000895</t>
+          <t>HMDB0001925</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>C01996</t>
+          <t>C01588</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>RM0041817</t>
+          <t>RM0052815</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -67339,16 +67614,16 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>841</v>
+        <v>808</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Phenylalanylphenylalanine</t>
+          <t>geranial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GKZIWHRNKRBEOH-UHFFFAOYSA-N</t>
+          <t>WTEVQBCEXWBHNA-JXMROGBWSA-N</t>
         </is>
       </c>
       <c r="D63">
@@ -67356,62 +67631,62 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Phenylalanylphenylalanine</t>
+          <t>geranial</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Phe-Phe</t>
+          <t>Citral</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>C18H20N2O3</t>
+          <t>C10H16O</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>312.1474</t>
+          <t>152.1201</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Prenol Lipids</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Amino acids and peptides</t>
+          <t>Isoprenoids</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Dipeptides</t>
+          <t>C10 isoprenoids</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>GKZIWHRNKRBEOH-HOTGVXAUSA-N</t>
+          <t>WTEVQBCEXWBHNA-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>6993090</t>
+          <t>8843</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>72723</t>
+          <t>23316</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>HMDB0013302</t>
+          <t>HMDB0250303</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>RM0137544</t>
+          <t>RM0015070</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -67427,16 +67702,16 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>871</v>
+        <v>830</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Laurolactam</t>
+          <t>Acetylcholine</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>QKTZBZWNADPFOL-BNFZFUHLSA-N</t>
+          <t>JHPNVNIEXXLNTR-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D64">
@@ -67444,57 +67719,67 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Laurolactam</t>
+          <t>Acetylcholine</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Azacyclotridecan-2-one</t>
+          <t>Acetylcholine</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>C12H23NO</t>
+          <t>C7H16NO2</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>197.178</t>
+          <t>146.1181</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Polyketides</t>
+          <t>Organic nitrogen compounds</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Macrolides</t>
+          <t>Cholines</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Macrolactams</t>
+          <t>Acyl cholines</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>JHWNWJKBPDFINM-UHFFFAOYSA-N</t>
+          <t>OIPILFWXSMYKGL-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>172332</t>
+          <t>15355</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>HMDB0000895</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>C01996</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>RM0200479</t>
+          <t>RM0041817</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -67510,16 +67795,16 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>877</v>
+        <v>841</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dambonitol</t>
+          <t>Phenylalanylphenylalanine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MMCIFJWGSIWJLP-RRNBHUGPSA-N</t>
+          <t>GKZIWHRNKRBEOH-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D65">
@@ -67527,62 +67812,62 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dambonitol</t>
+          <t>Phenylalanylphenylalanine</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dambonitol</t>
+          <t>Phe-Phe</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C8H16O6</t>
+          <t>C18H20N2O3</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>208.0947</t>
+          <t>312.1474</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Organic oxygen compounds</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Alcohols and polyols</t>
+          <t>Amino acids and peptides</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Cyclitols</t>
+          <t>Dipeptides</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>MMCIFJWGSIWJLP-XAMPRYAMSA-N</t>
+          <t>GKZIWHRNKRBEOH-HOTGVXAUSA-N</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>21627888</t>
+          <t>6993090</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>173588</t>
+          <t>72723</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>HMDB0033942</t>
+          <t>HMDB0013302</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>RM0224280</t>
+          <t>RM0137544</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -67598,16 +67883,16 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>881</v>
+        <v>871</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ecgonine</t>
+          <t>Laurolactam</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PHMBVCPLDPDESM-RLXKETGRSA-N</t>
+          <t>QKTZBZWNADPFOL-BNFZFUHLSA-N</t>
         </is>
       </c>
       <c r="D66">
@@ -67615,72 +67900,62 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ecgonine</t>
+          <t>Laurolactam</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ecgonine</t>
+          <t>Azacyclotridecan-2-one</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>C9H15NO3</t>
+          <t>C12H23NO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>185.1052</t>
+          <t>197.178</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Alkaloids</t>
+          <t>Polyketides</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Ornithine alkaloids</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Tropane alkaloids</t>
+          <t>Macrolactams</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>PHMBVCPLDPDESM-FKSUSPILSA-N</t>
+          <t>JHWNWJKBPDFINM-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>91460</t>
+          <t>13690</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>4743</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>HMDB0006548</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>C10858</t>
+          <t>172332</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>RM0013096</t>
+          <t>RM0200479</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Connectivity match</t>
+          <t>Mismatch</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -67691,16 +67966,16 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tetranor 12-HETE</t>
+          <t>Dambonitol</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>KBOVKDIBOBQLRS-ONCCEEIJSA-N</t>
+          <t>MMCIFJWGSIWJLP-RRNBHUGPSA-N</t>
         </is>
       </c>
       <c r="D67">
@@ -67708,62 +67983,62 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tetranor 12-HETE</t>
+          <t>Dambonitol</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tetranor-12R-HETE</t>
+          <t>Dambonitol</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>C16H26O3</t>
+          <t>C8H16O6</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>266.1882</t>
+          <t>208.0947</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Fatty Acyls</t>
+          <t>Organic oxygen compounds</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Eicosanoids</t>
+          <t>Alcohols and polyols</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>HETE</t>
+          <t>Cyclitols</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>KBOVKDIBOBQLRS-QCNAHCIUSA-N</t>
+          <t>MMCIFJWGSIWJLP-XAMPRYAMSA-N</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>5282970</t>
+          <t>21627888</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>72605</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>LMFA01050143</t>
+          <t>173588</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>HMDB0033942</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>RM0153662</t>
+          <t>RM0224280</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -67779,84 +68054,84 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>940</v>
+        <v>881</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>L-Phenylalanine</t>
+          <t>Ecgonine</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>COLNVLDHVKWLRT-UHFFFAOYSA-N</t>
+          <t>PHMBVCPLDPDESM-RLXKETGRSA-N</t>
         </is>
       </c>
       <c r="D68">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>L-Phenylalanine</t>
+          <t>Ecgonine</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Phenylalanine</t>
+          <t>Ecgonine</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>C9H11NO2</t>
+          <t>C9H15NO3</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>165.079</t>
+          <t>185.1052</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Alkaloids</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Amino acids and peptides</t>
+          <t>Ornithine alkaloids</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Amino acids</t>
+          <t>Tropane alkaloids</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>COLNVLDHVKWLRT-QMMMGPOBSA-N</t>
+          <t>PHMBVCPLDPDESM-FKSUSPILSA-N</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>6140</t>
+          <t>91460</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>28044</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>HMDB0000159</t>
+          <t>HMDB0006548</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>C00079</t>
+          <t>C10858</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>RM0135897</t>
+          <t>RM0013096</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -67872,79 +68147,79 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>941</v>
+        <v>885</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>His-Trp</t>
+          <t>Tetranor 12-HETE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FBTYOQIYBULKEH-UHFFFAOYSA-N</t>
+          <t>KBOVKDIBOBQLRS-ONCCEEIJSA-N</t>
         </is>
       </c>
       <c r="D69">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>His-Trp</t>
+          <t>Tetranor 12-HETE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>His-Trp</t>
+          <t>Tetranor-12R-HETE</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>C17H19N5O3</t>
+          <t>C16H26O3</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>341.1488</t>
+          <t>266.1882</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Fatty Acyls</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Amino acids and peptides</t>
+          <t>Eicosanoids</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Dipeptides</t>
+          <t>HETE</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>FBTYOQIYBULKEH-ZFWWWQNUSA-N</t>
+          <t>KBOVKDIBOBQLRS-QCNAHCIUSA-N</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>7009650</t>
+          <t>5282970</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>74058</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>HMDB0028896</t>
+          <t>72605</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>LMFA01050143</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>RM0022480</t>
+          <t>RM0153662</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -67960,16 +68235,16 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>956</v>
+        <v>940</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[(4Z)-5-(Methylsulfanyl)-4-penten-2-yn-1-yl]benzene</t>
+          <t>L-Phenylalanine</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BQJDNQQWNLQSGB-XFFZJAGNSA-N</t>
+          <t>COLNVLDHVKWLRT-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D70">
@@ -67977,72 +68252,72 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>[(4Z)-5-(Methylsulfanyl)-4-penten-2-yn-1-yl]benzene</t>
+          <t>L-Phenylalanine</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Benzene</t>
+          <t>Phenylalanine</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>C6H6</t>
+          <t>C9H11NO2</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>78.0469</t>
+          <t>165.079</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Benzenoids</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Benzenes</t>
+          <t>Amino acids and peptides</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Other benzenes</t>
+          <t>Amino acids</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>UHOVQNZJYSORNB-UHFFFAOYSA-N</t>
+          <t>COLNVLDHVKWLRT-QMMMGPOBSA-N</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>16716</t>
+          <t>28044</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>HMDB0001505</t>
+          <t>HMDB0000159</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>C01407</t>
+          <t>C00079</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>RM0049371</t>
+          <t>RM0135897</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -68053,16 +68328,16 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>959</v>
+        <v>941</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Testosterone sulfate</t>
+          <t>His-Trp</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CZWCKYRVOZZJNM-USOAJAOKSA-N</t>
+          <t>FBTYOQIYBULKEH-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D71">
@@ -68070,72 +68345,67 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Testosterone sulfate</t>
+          <t>His-Trp</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Testosterone sulfate</t>
+          <t>His-Trp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>C19H28O5S</t>
+          <t>C17H19N5O3</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>368.1657</t>
+          <t>341.1488</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Sterol Lipids</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Steroids</t>
+          <t>Amino acids and peptides</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>C19 Steroids</t>
+          <t>Dipeptides</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>WAQBISPOEAOCOG-DYKIIFRCSA-N</t>
+          <t>FBTYOQIYBULKEH-ZFWWWQNUSA-N</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>119207</t>
+          <t>7009650</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>84094</t>
+          <t>74058</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>HMDB0002833</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>LMST05020032</t>
+          <t>HMDB0028896</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>RM0126068</t>
+          <t>RM0022480</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -68146,16 +68416,16 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DL-Stachydrine</t>
+          <t>[(4Z)-5-(Methylsulfanyl)-4-penten-2-yn-1-yl]benzene</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CMUNUTVVOOHQPW-LURJTMIESA-N</t>
+          <t>BQJDNQQWNLQSGB-XFFZJAGNSA-N</t>
         </is>
       </c>
       <c r="D72">
@@ -68163,72 +68433,72 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>DL-Stachydrine</t>
+          <t>[(4Z)-5-(Methylsulfanyl)-4-penten-2-yn-1-yl]benzene</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stachydrine</t>
+          <t>Benzene</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>C7H14NO2</t>
+          <t>C6H6</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>144.1025</t>
+          <t>78.0469</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Benzenoids</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Amino acids and peptides</t>
+          <t>Benzenes</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Amino acids</t>
+          <t>Other benzenes</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CMUNUTVVOOHQPW-ZCFIWIBFSA-O</t>
+          <t>UHOVQNZJYSORNB-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>7016563</t>
+          <t>241</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>35280</t>
+          <t>16716</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>HMDB0240479</t>
+          <t>HMDB0001505</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>C10172</t>
+          <t>C01407</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>RM0159324</t>
+          <t>RM0049371</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Connectivity match</t>
+          <t>Mismatch</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -68239,16 +68509,16 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>976</v>
+        <v>959</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3-hydroxyoctanoylcarnitine</t>
+          <t>Testosterone sulfate</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LUBMSOHGUAAXAM-UHFFFAOYSA-N</t>
+          <t>CZWCKYRVOZZJNM-USOAJAOKSA-N</t>
         </is>
       </c>
       <c r="D73">
@@ -68256,67 +68526,72 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>3-hydroxyoctanoylcarnitine</t>
+          <t>Testosterone sulfate</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CAR 8:0;3OH</t>
+          <t>Testosterone sulfate</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>C15H29NO5</t>
+          <t>C19H28O5S</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>303.2046</t>
+          <t>368.1657</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Fatty Acyls</t>
+          <t>Sterol Lipids</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Fatty esters</t>
+          <t>Steroids</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Acyl carnitines</t>
+          <t>C19 Steroids</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>LUBMSOHGUAAXAM-ZGTCLIOFSA-N</t>
+          <t>WAQBISPOEAOCOG-DYKIIFRCSA-N</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>86583357</t>
+          <t>119207</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>84100</t>
+          <t>84094</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>HMDB0061634</t>
+          <t>HMDB0002833</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>LMST05020032</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>RM0154062</t>
+          <t>RM0126068</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Connectivity match</t>
+          <t>Mismatch</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -68327,16 +68602,16 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>980</v>
+        <v>964</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ecgonine</t>
+          <t>DL-Stachydrine</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PHMBVCPLDPDESM-RLXKETGRSA-N</t>
+          <t>CMUNUTVVOOHQPW-LURJTMIESA-N</t>
         </is>
       </c>
       <c r="D74">
@@ -68344,67 +68619,67 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ecgonine</t>
+          <t>DL-Stachydrine</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ecgonine</t>
+          <t>Stachydrine</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C9H15NO3</t>
+          <t>C7H14NO2</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>185.1052</t>
+          <t>144.1025</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Alkaloids</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Ornithine alkaloids</t>
+          <t>Amino acids and peptides</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Tropane alkaloids</t>
+          <t>Amino acids</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>PHMBVCPLDPDESM-FKSUSPILSA-N</t>
+          <t>CMUNUTVVOOHQPW-ZCFIWIBFSA-O</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>91460</t>
+          <t>7016563</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>35280</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>HMDB0006548</t>
+          <t>HMDB0240479</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>C10858</t>
+          <t>C10172</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>RM0013096</t>
+          <t>RM0159324</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -68420,39 +68695,39 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>1042</v>
+        <v>976</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Glutarylcarnitine</t>
+          <t>3-hydroxyoctanoylcarnitine</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NXJAXUYOQLTISD-VIFPVBQESA-N</t>
+          <t>LUBMSOHGUAAXAM-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D75">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Glutarylcarnitine</t>
+          <t>3-hydroxyoctanoylcarnitine</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CAR DC5:0</t>
+          <t>CAR 8:0;3OH</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C12H21NO6</t>
+          <t>C15H29NO5</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>275.1369</t>
+          <t>303.2046</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -68472,32 +68747,27 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>NXJAXUYOQLTISD-SECBINFHSA-N</t>
+          <t>LUBMSOHGUAAXAM-ZGTCLIOFSA-N</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>71317118</t>
+          <t>86583357</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>165628</t>
+          <t>84100</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>HMDB0013130</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>LMFA07070066</t>
+          <t>HMDB0061634</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>RM0153962</t>
+          <t>RM0154062</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -68513,89 +68783,89 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>1085</v>
+        <v>980</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>4-Hydroxyphenylpyruvic acid</t>
+          <t>Ecgonine</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BSYNRYMUTXBXSQ-UHFFFAOYSA-N</t>
+          <t>PHMBVCPLDPDESM-RLXKETGRSA-N</t>
         </is>
       </c>
       <c r="D76">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>4-Hydroxyphenylpyruvic acid</t>
+          <t>Ecgonine</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>4-Hydroxyphenylpyruvic acid</t>
+          <t>Ecgonine</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>C9H8O4</t>
+          <t>C9H15NO3</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>180.0423</t>
+          <t>185.1052</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Alkaloids</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Phenylpropanoids</t>
+          <t>Ornithine alkaloids</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Cinnamic acids</t>
+          <t>Tropane alkaloids</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>KKADPXVIOXHVKN-UHFFFAOYSA-N</t>
+          <t>PHMBVCPLDPDESM-FKSUSPILSA-N</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>91460</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>15999</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>HMDB0000707</t>
+          <t>HMDB0006548</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>C01179</t>
+          <t>C10858</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>RM0020531</t>
+          <t>RM0013096</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -68606,16 +68876,16 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>1100</v>
+        <v>1042</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Leu-Leu</t>
+          <t>Glutarylcarnitine</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LCPYQJIKPJDLLB-UHFFFAOYSA-N</t>
+          <t>NXJAXUYOQLTISD-VIFPVBQESA-N</t>
         </is>
       </c>
       <c r="D77">
@@ -68623,67 +68893,67 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Leu-Leu</t>
+          <t>Glutarylcarnitine</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Leu-Leu</t>
+          <t>CAR DC5:0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>C12H24N2O3</t>
+          <t>C12H21NO6</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>244.1787</t>
+          <t>275.1369</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Fatty Acyls</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Amino acids and peptides</t>
+          <t>Fatty esters</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Dipeptides</t>
+          <t>Acyl carnitines</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>LCPYQJIKPJDLLB-UWVGGRQHSA-N</t>
+          <t>NXJAXUYOQLTISD-SECBINFHSA-N</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>76807</t>
+          <t>71317118</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>73531</t>
+          <t>165628</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>HMDB0028933</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>C11332</t>
+          <t>HMDB0013130</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>LMFA07070066</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>RM0129935</t>
+          <t>RM0153962</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -68699,39 +68969,39 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>1103</v>
+        <v>1085</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>L-(-)-Serine</t>
+          <t>4-Hydroxyphenylpyruvic acid</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MTCFGRXMJLQNBG-UHFFFAOYSA-N</t>
+          <t>BSYNRYMUTXBXSQ-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D78">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>L-(-)-Serine</t>
+          <t>4-Hydroxyphenylpyruvic acid</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Serine</t>
+          <t>4-Hydroxyphenylpyruvic acid</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>C3H7NO3</t>
+          <t>C9H8O4</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>105.0426</t>
+          <t>180.0423</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -68741,47 +69011,47 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Amino acids and peptides</t>
+          <t>Phenylpropanoids</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Amino acids</t>
+          <t>Cinnamic acids</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>MTCFGRXMJLQNBG-REOHCLBHSA-N</t>
+          <t>KKADPXVIOXHVKN-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>979</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>17822</t>
+          <t>15999</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>HMDB0000187</t>
+          <t>HMDB0000707</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>C00065</t>
+          <t>C01179</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>RM0032433</t>
+          <t>RM0020531</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Connectivity match</t>
+          <t>Mismatch</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -68792,39 +69062,39 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>1157</v>
+        <v>1100</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3-(3,4,5-trimethoxyphenyl)propanoic acid</t>
+          <t>Leu-Leu</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FLKPEMZONWLCSK-UHFFFAOYSA-N</t>
+          <t>LCPYQJIKPJDLLB-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D79">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>3-(3,4,5-trimethoxyphenyl)propanoic acid</t>
+          <t>Leu-Leu</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>3-(3,4,5-Trimethoxyphenyl)propanoic acid</t>
+          <t>Leu-Leu</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>C12H16O5</t>
+          <t>C12H24N2O3</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>240.0998</t>
+          <t>244.1787</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -68834,42 +69104,47 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Phenylpropanoids</t>
+          <t>Amino acids and peptides</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Cinnamic acids</t>
+          <t>Dipeptides</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>ZCYXGVJUZBKJAI-UHFFFAOYSA-N</t>
+          <t>LCPYQJIKPJDLLB-UWVGGRQHSA-N</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>64860</t>
+          <t>76807</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>583580</t>
+          <t>73531</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>HMDB0030254</t>
+          <t>HMDB0028933</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>C11332</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>RM0226646</t>
+          <t>RM0129935</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -68880,16 +69155,16 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>1166</v>
+        <v>1103</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Atenolol</t>
+          <t>L-(-)-Serine</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>METKIMKYRPQLGS-UHFFFAOYSA-N</t>
+          <t>MTCFGRXMJLQNBG-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D80">
@@ -68897,62 +69172,67 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atenolol</t>
+          <t>L-(-)-Serine</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Atenolol</t>
+          <t>Serine</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>C14H22N2O3</t>
+          <t>C3H7NO3</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>266.163</t>
+          <t>105.0426</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Benzenoids</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Phenols</t>
+          <t>Amino acids and peptides</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Phenol ethers</t>
+          <t>Amino acids</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>METKIMKYRPQLGS-LBPRGKRZSA-N</t>
+          <t>MTCFGRXMJLQNBG-REOHCLBHSA-N</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>175540</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>HMDB0001924</t>
+          <t>HMDB0000187</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>C00065</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>RM0003835</t>
+          <t>RM0032433</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -68968,16 +69248,16 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>1172</v>
+        <v>1157</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[(4Z)-5-(Methylsulfanyl)-4-penten-2-yn-1-yl]benzene</t>
+          <t>3-(3,4,5-trimethoxyphenyl)propanoic acid</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BQJDNQQWNLQSGB-XFFZJAGNSA-N</t>
+          <t>FLKPEMZONWLCSK-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D81">
@@ -68985,67 +69265,62 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>[(4Z)-5-(Methylsulfanyl)-4-penten-2-yn-1-yl]benzene</t>
+          <t>3-(3,4,5-trimethoxyphenyl)propanoic acid</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Benzene</t>
+          <t>3-(3,4,5-Trimethoxyphenyl)propanoic acid</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>C6H6</t>
+          <t>C12H16O5</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>78.0469</t>
+          <t>240.0998</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Benzenoids</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Benzenes</t>
+          <t>Phenylpropanoids</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Other benzenes</t>
+          <t>Cinnamic acids</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>UHOVQNZJYSORNB-UHFFFAOYSA-N</t>
+          <t>ZCYXGVJUZBKJAI-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>64860</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>16716</t>
+          <t>583580</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>HMDB0001505</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>C01407</t>
+          <t>HMDB0030254</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>RM0049371</t>
+          <t>RM0226646</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -69061,16 +69336,16 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>1179</v>
+        <v>1166</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ceramide (d18:1/16:0)</t>
+          <t>Atenolol</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>YDNKGFDKKRUKPY-UHFFFAOYSA-N</t>
+          <t>METKIMKYRPQLGS-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D82">
@@ -69078,72 +69353,62 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ceramide (d18:1/16:0)</t>
+          <t>Atenolol</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cer 18:1;O2/16:0</t>
+          <t>Atenolol</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>C34H67NO3</t>
+          <t>C14H22N2O3</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>537.5121</t>
+          <t>266.163</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Sphingolipids</t>
+          <t>Benzenoids</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Ceramides</t>
+          <t>Phenols</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Cer</t>
+          <t>Phenol ethers</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>YDNKGFDKKRUKPY-TURZORIXSA-N</t>
+          <t>METKIMKYRPQLGS-LBPRGKRZSA-N</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>5283564</t>
+          <t>175540</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>72959</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>HMDB0004949</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>LMSP02010004</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>C00422</t>
+          <t>HMDB0001924</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>RM0135485</t>
+          <t>RM0003835</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -69159,84 +69424,89 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>1217</v>
+        <v>1172</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>(2E)-3-(3,4-Dimethoxyphenyl)acrylic acid</t>
+          <t>[(4Z)-5-(Methylsulfanyl)-4-penten-2-yn-1-yl]benzene</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HJBWJAPEBGSQPR-UHFFFAOYSA-N</t>
+          <t>BQJDNQQWNLQSGB-XFFZJAGNSA-N</t>
         </is>
       </c>
       <c r="D83">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>(2E)-3-(3,4-Dimethoxyphenyl)acrylic acid</t>
+          <t>[(4Z)-5-(Methylsulfanyl)-4-penten-2-yn-1-yl]benzene</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>3-(3,4-Dimethoxyphenyl)-2-propenoic acid</t>
+          <t>Benzene</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>C11H12O4</t>
+          <t>C6H6</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>208.0736</t>
+          <t>78.0469</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Benzenoids</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Phenylpropanoids</t>
+          <t>Benzenes</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Cinnamic acids</t>
+          <t>Other benzenes</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>HJBWJAPEBGSQPR-GQCTYLIASA-N</t>
+          <t>UHOVQNZJYSORNB-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>717531</t>
+          <t>241</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>86549</t>
+          <t>16716</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>HMDB0034315</t>
+          <t>HMDB0001505</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>C01407</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>RM0139025</t>
+          <t>RM0049371</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Connectivity match</t>
+          <t>Mismatch</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -69247,79 +69517,89 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>1244</v>
+        <v>1179</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Leu-Val</t>
+          <t>Ceramide (d18:1/16:0)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MDSUKZSLOATHMH-UHFFFAOYSA-N</t>
+          <t>YDNKGFDKKRUKPY-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D84">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Leu-Val</t>
+          <t>Ceramide (d18:1/16:0)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Leu-Val</t>
+          <t>Cer 18:1;O2/16:0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>C11H22N2O3</t>
+          <t>C34H67NO3</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>230.163</t>
+          <t>537.5121</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Sphingolipids</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Amino acids and peptides</t>
+          <t>Ceramides</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Dipeptides</t>
+          <t>Cer</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>MDSUKZSLOATHMH-IUCAKERBSA-N</t>
+          <t>YDNKGFDKKRUKPY-TURZORIXSA-N</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>6993116</t>
+          <t>5283564</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>73579</t>
+          <t>72959</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>HMDB0028942</t>
+          <t>HMDB0004949</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>LMSP02010004</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>C00422</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>RM0137534</t>
+          <t>RM0135485</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -69335,16 +69615,16 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>1262</v>
+        <v>1217</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3-hydroxyoctanoylcarnitine</t>
+          <t>(2E)-3-(3,4-Dimethoxyphenyl)acrylic acid</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LUBMSOHGUAAXAM-UHFFFAOYSA-N</t>
+          <t>HJBWJAPEBGSQPR-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D85">
@@ -69352,62 +69632,62 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>3-hydroxyoctanoylcarnitine</t>
+          <t>(2E)-3-(3,4-Dimethoxyphenyl)acrylic acid</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CAR 8:0;3OH</t>
+          <t>3-(3,4-Dimethoxyphenyl)-2-propenoic acid</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>C15H29NO5</t>
+          <t>C11H12O4</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>303.2046</t>
+          <t>208.0736</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Fatty Acyls</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Fatty esters</t>
+          <t>Phenylpropanoids</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Acyl carnitines</t>
+          <t>Cinnamic acids</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>LUBMSOHGUAAXAM-ZGTCLIOFSA-N</t>
+          <t>HJBWJAPEBGSQPR-GQCTYLIASA-N</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>86583357</t>
+          <t>717531</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>84100</t>
+          <t>86549</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>HMDB0061634</t>
+          <t>HMDB0034315</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>RM0154062</t>
+          <t>RM0139025</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -69423,89 +69703,84 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>1328</v>
+        <v>1244</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>urobilinogen</t>
+          <t>Leu-Val</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OBHRVMZSZIDDEK-UHFFFAOYSA-N</t>
+          <t>MDSUKZSLOATHMH-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D86">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>urobilinogen</t>
+          <t>Leu-Val</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>D-Urobilinogen</t>
+          <t>Leu-Val</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>C33H42N4O6</t>
+          <t>C11H22N2O3</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>590.3104</t>
+          <t>230.163</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Organoheterocyclic compounds</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Bilirubins</t>
+          <t>Amino acids and peptides</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Bilirubins</t>
+          <t>Dipeptides</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>KSQFFJKKJAEKTB-UHFFFAOYSA-N</t>
+          <t>MDSUKZSLOATHMH-IUCAKERBSA-N</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>440784</t>
+          <t>6993116</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>73579</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>HMDB0004158</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>C05791</t>
+          <t>HMDB0028942</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>RM0030049</t>
+          <t>RM0137534</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -69516,79 +69791,79 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>1379</v>
+        <v>1262</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Leu-Val</t>
+          <t>3-hydroxyoctanoylcarnitine</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MDSUKZSLOATHMH-UHFFFAOYSA-N</t>
+          <t>LUBMSOHGUAAXAM-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D87">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Leu-Val</t>
+          <t>3-hydroxyoctanoylcarnitine</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Leu-Val</t>
+          <t>CAR 8:0;3OH</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>C11H22N2O3</t>
+          <t>C15H29NO5</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>230.163</t>
+          <t>303.2046</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Fatty Acyls</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Amino acids and peptides</t>
+          <t>Fatty esters</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Dipeptides</t>
+          <t>Acyl carnitines</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>MDSUKZSLOATHMH-IUCAKERBSA-N</t>
+          <t>LUBMSOHGUAAXAM-ZGTCLIOFSA-N</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>6993116</t>
+          <t>86583357</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>73579</t>
+          <t>84100</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>HMDB0028942</t>
+          <t>HMDB0061634</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>RM0137534</t>
+          <t>RM0154062</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -69604,16 +69879,16 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>1383</v>
+        <v>1328</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>10-Hydroxydecanoic acid</t>
+          <t>urobilinogen</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FYSSBMZUBSBFJL-UHFFFAOYSA-N</t>
+          <t>OBHRVMZSZIDDEK-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D88">
@@ -69621,72 +69896,67 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>10-Hydroxydecanoic acid</t>
+          <t>urobilinogen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>10-Hydroxydecanoic acid</t>
+          <t>D-Urobilinogen</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>C10H20O3</t>
+          <t>C33H42N4O6</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>188.1412</t>
+          <t>590.3104</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Fatty Acyls</t>
+          <t>Organoheterocyclic compounds</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Fatty acids</t>
+          <t>Bilirubins</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Hydroxy FA</t>
+          <t>Bilirubins</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>YJCJVMMDTBEITC-UHFFFAOYSA-N</t>
+          <t>KSQFFJKKJAEKTB-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>74300</t>
+          <t>440784</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>17409</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>HMDB0244272</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>LMFA01050033</t>
+          <t>HMDB0004158</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>C02774</t>
+          <t>C05791</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>RM0153657</t>
+          <t>RM0030049</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -69702,84 +69972,79 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>1413</v>
+        <v>1379</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>(R)-3-hydroxybutyrylcarnitine</t>
+          <t>Leu-Val</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>UEFRDQSMQXDWTO-YGPZHTELSA-N</t>
+          <t>MDSUKZSLOATHMH-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D89">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(R)-3-hydroxybutyrylcarnitine</t>
+          <t>Leu-Val</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CAR 4:0;3OH</t>
+          <t>Leu-Val</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>C11H21NO5</t>
+          <t>C11H22N2O3</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>247.142</t>
+          <t>230.163</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Fatty Acyls</t>
+          <t>Organic acids</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Fatty esters</t>
+          <t>Amino acids and peptides</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Acyl carnitines</t>
+          <t>Dipeptides</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>UEFRDQSMQXDWTO-GKAPJAKFSA-N</t>
+          <t>MDSUKZSLOATHMH-IUCAKERBSA-N</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>53481617</t>
+          <t>6993116</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>72995</t>
+          <t>73579</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>HMDB0013127</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>LMFA07070071</t>
+          <t>HMDB0028942</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>RM0154200</t>
+          <t>RM0137534</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -69795,79 +70060,94 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>1425</v>
+        <v>1383</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ecgonine methyl ester</t>
+          <t>10-Hydroxydecanoic acid</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>QIQNNBXHAYSQRY-ABIFROTESA-N</t>
+          <t>FYSSBMZUBSBFJL-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D90">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ecgonine methyl ester</t>
+          <t>10-Hydroxydecanoic acid</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ecgonine methyl ester</t>
+          <t>10-Hydroxydecanoic acid</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>C10H17NO3</t>
+          <t>C10H20O3</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>199.1208</t>
+          <t>188.1412</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Alkaloids</t>
+          <t>Fatty Acyls</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Ornithine alkaloids</t>
+          <t>Fatty acids</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Tropane alkaloids</t>
+          <t>Hydroxy FA</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>QIQNNBXHAYSQRY-UYXSQOIJSA-N</t>
+          <t>YJCJVMMDTBEITC-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>104904</t>
+          <t>74300</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>31529</t>
+          <t>17409</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>HMDB0244272</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>LMFA01050033</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>C02774</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>RM0204062</t>
+          <t>RM0153657</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Connectivity match</t>
+          <t>Mismatch</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
@@ -69878,16 +70158,16 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>1478</v>
+        <v>1413</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mannitol 1-phosphate</t>
+          <t>(R)-3-hydroxybutyrylcarnitine</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GACTWZZMVMUKNG-UHFFFAOYSA-N</t>
+          <t>UEFRDQSMQXDWTO-YGPZHTELSA-N</t>
         </is>
       </c>
       <c r="D91">
@@ -69895,67 +70175,67 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mannitol 1-phosphate</t>
+          <t>(R)-3-hydroxybutyrylcarnitine</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mannitol 1-phosphate</t>
+          <t>CAR 4:0;3OH</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>C6H15O9P</t>
+          <t>C11H21NO5</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>262.0454</t>
+          <t>247.142</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Carbohydrates</t>
+          <t>Fatty Acyls</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Monosaccharides</t>
+          <t>Fatty esters</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Hexose phosphates</t>
+          <t>Acyl carnitines</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>GACTWZZMVMUKNG-KVTDHHQDSA-N</t>
+          <t>UEFRDQSMQXDWTO-GKAPJAKFSA-N</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>130418</t>
+          <t>53481617</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>16298</t>
+          <t>72995</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>HMDB0001530</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>C00644</t>
+          <t>HMDB0013127</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>LMFA07070071</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>RM0155922</t>
+          <t>RM0154200</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -69971,79 +70251,74 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>1504</v>
+        <v>1425</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>L-γ-Glutamyl-L-valine</t>
+          <t>Ecgonine methyl ester</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AQAKHZVPOOGUCK-UHFFFAOYSA-N</t>
+          <t>QIQNNBXHAYSQRY-ABIFROTESA-N</t>
         </is>
       </c>
       <c r="D92">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>L-γ-Glutamyl-L-valine</t>
+          <t>Ecgonine methyl ester</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>gamma-Glutamylvaline</t>
+          <t>Ecgonine methyl ester</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>C10H18N2O5</t>
+          <t>C10H17NO3</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>246.1216</t>
+          <t>199.1208</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Organic acids</t>
+          <t>Alkaloids</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Amino acids and peptides</t>
+          <t>Ornithine alkaloids</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Dipeptides</t>
+          <t>Tropane alkaloids</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>AQAKHZVPOOGUCK-XPUUQOCRSA-N</t>
+          <t>QIQNNBXHAYSQRY-UYXSQOIJSA-N</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>7015683</t>
+          <t>104904</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>68848</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>HMDB0011172</t>
+          <t>31529</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>RM0137112</t>
+          <t>RM0204062</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -70059,79 +70334,89 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>1565</v>
+        <v>1478</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Norbenzoylecgonine</t>
+          <t>Mannitol 1-phosphate</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ONPUKGULNMQBLF-UHFFFAOYSA-N</t>
+          <t>GACTWZZMVMUKNG-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D93">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Norbenzoylecgonine</t>
+          <t>Mannitol 1-phosphate</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Benzoylnorecgonine</t>
+          <t>Mannitol 1-phosphate</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>C15H17NO4</t>
+          <t>C6H15O9P</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>275.1158</t>
+          <t>262.0454</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Alkaloids</t>
+          <t>Carbohydrates</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Ornithine alkaloids</t>
+          <t>Monosaccharides</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Tropane alkaloids</t>
+          <t>Hexose phosphates</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CMYJDRSCSOXYHG-UHFFFAOYSA-N</t>
+          <t>GACTWZZMVMUKNG-KVTDHHQDSA-N</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>415793</t>
+          <t>130418</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>16298</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>HMDB0249054</t>
+          <t>HMDB0001530</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>C00644</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>RM0188079</t>
+          <t>RM0155922</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Connectivity match</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -70142,16 +70427,16 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>1600</v>
+        <v>1504</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>trp-lys</t>
+          <t>L-γ-Glutamyl-L-valine</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DZHDVYLBNKMLMB-UHFFFAOYSA-N</t>
+          <t>AQAKHZVPOOGUCK-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="D94">
@@ -70159,70 +70444,241 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>L-γ-Glutamyl-L-valine</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>gamma-Glutamylvaline</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>C10H18N2O5</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>246.1216</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Organic acids</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Amino acids and peptides</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Dipeptides</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>AQAKHZVPOOGUCK-XPUUQOCRSA-N</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>7015683</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>68848</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>HMDB0011172</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>RM0137112</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Connectivity match</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>1565</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Norbenzoylecgonine</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ONPUKGULNMQBLF-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="D95">
+        <v>16</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Norbenzoylecgonine</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Benzoylnorecgonine</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>C15H17NO4</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>275.1158</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Alkaloids</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Ornithine alkaloids</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Tropane alkaloids</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>CMYJDRSCSOXYHG-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>415793</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>HMDB0249054</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>RM0188079</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>1600</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
           <t>trp-lys</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>DZHDVYLBNKMLMB-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="D96">
+        <v>16</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>trp-lys</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>Trp-Lys</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>C17H24N4O3</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>332.1848</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>Organic acids</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>Amino acids and peptides</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>Dipeptides</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>DZHDVYLBNKMLMB-ZFWWWQNUSA-N</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>6452501</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>74872</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>HMDB0029088</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="R96" t="inlineStr">
         <is>
           <t>RM0137566</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
+      <c r="S96" t="inlineStr">
         <is>
           <t>Connectivity match</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr">
+      <c r="T96" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
@@ -80083,13 +80539,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19013B00-F964-45BA-BBD5-0A7B6686C56E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A300B35-99A5-4A4E-B1E7-3837A9DDE42F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E573E8D1-5351-4E49-9AFF-45DA47BD4E0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7EFF8AC-C551-4229-8FE0-4180324F39EE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56C7D857-8973-44B2-8DB6-9F10CF14AE79}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8232A4B8-E4BF-485C-8BC6-03C65D300F94}"/>
 </file>